--- a/integrated/output/통합_AI클라우드_보안위협_매트릭스_v1.xlsx
+++ b/integrated/output/통합_AI클라우드_보안위협_매트릭스_v1.xlsx
@@ -64250,7 +64250,7 @@
       </c>
       <c r="K222" s="45" t="inlineStr">
         <is>
-          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음</t>
+          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음 (T1550.001·.004를 횡적 이동 전술에서 이동)</t>
         </is>
       </c>
     </row>
@@ -64307,7 +64307,7 @@
       </c>
       <c r="K223" s="45" t="inlineStr">
         <is>
-          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음</t>
+          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음 (T1550.001·.004를 횡적 이동 전술에서 이동)</t>
         </is>
       </c>
     </row>
@@ -64364,7 +64364,7 @@
       </c>
       <c r="K224" s="45" t="inlineStr">
         <is>
-          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음</t>
+          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음 (T1550.001·.004를 횡적 이동 전술에서 이동)</t>
         </is>
       </c>
     </row>
@@ -64421,7 +64421,7 @@
       </c>
       <c r="K225" s="45" t="inlineStr">
         <is>
-          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음</t>
+          <t>토큰·쿠키 탈취(자격증명 접근)와 탈취 자료 사용(횡적 이동)은 한 공격 흐름의 연속 단계이며 토큰 수명·바인딩이라는 같은 통제를 받음 (T1550.001·.004를 횡적 이동 전술에서 이동)</t>
         </is>
       </c>
     </row>
